--- a/ban-giao-khach-hang/file-dien-du-lieu/5_Thong_tin_cua_hang.xlsx
+++ b/ban-giao-khach-hang/file-dien-du-lieu/5_Thong_tin_cua_hang.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>📋 HƯỚNG DẪN ĐIỀN THÔNG TIN CỬA HÀNG</t>
   </si>
@@ -20,7 +20,7 @@
     <t>Mục đích</t>
   </si>
   <si>
-    <t>Khai báo toàn bộ thông tin nhận diện &amp; nội dung trang chủ: logo, liên hệ, mạng xã hội, SEO, ảnh hero, câu chuyện thương hiệu.</t>
+    <t>Khai báo toàn bộ thông tin nhận diện &amp; nội dung trang chủ: logo, liên hệ, mạng xã hội, SEO, ảnh hero, câu chuyện thương hiệu, huy hiệu tin cậy.</t>
   </si>
   <si>
     <t>Cách điền</t>
@@ -32,25 +32,37 @@
     <t>Ảnh (logo, favicon, hero...)</t>
   </si>
   <si>
-    <t>Gửi kèm file ảnh cho bên kỹ thuật và ghi TÊN FILE vào ô tương ứng. Ảnh hero nên ngang, tối thiểu 1920x1080.</t>
+    <t>Ghi TÊN FILE (không dấu) vào ô tương ứng và gửi kèm ảnh. Ảnh hero nên ngang, tối thiểu 1920x1080. Favicon 32x32 hoặc .ico. Ảnh OG 1200x630.</t>
   </si>
   <si>
     <t>Song ngữ</t>
   </si>
   <si>
-    <t>Website hỗ trợ Tiếng Việt &amp; Tiếng Anh. Mục nào có (EN) là bản tiếng Anh — nếu không cần song ngữ có thể để trống, sẽ dùng bản tiếng Việt.</t>
+    <t>Website hỗ trợ Tiếng Việt &amp; Tiếng Anh. Mục có (EN) là bản tiếng Anh — để trống sẽ tự dùng bản tiếng Việt.</t>
   </si>
   <si>
     <t>Mạng xã hội</t>
   </si>
   <si>
-    <t>Chỉ điền link mạng xã hội đang dùng, còn lại để trống.</t>
+    <t>Chỉ điền link (bắt đầu https://) mạng xã hội đang dùng, còn lại để trống.</t>
+  </si>
+  <si>
+    <t>Email nhận báo giá</t>
+  </si>
+  <si>
+    <t>Email này vừa hiển thị liên hệ, vừa là nơi hệ thống gửi thông báo khi khách gửi yêu cầu báo giá.</t>
+  </si>
+  <si>
+    <t>Câu chuyện &amp; Huy hiệu</t>
+  </si>
+  <si>
+    <t>Nội dung Câu chuyện thương hiệu và Huy hiệu tin cậy được nạp khi khởi tạo. Muốn thay đổi về sau, vui lòng liên hệ đội kỹ thuật.</t>
   </si>
   <si>
     <t>Sau khi điền xong</t>
   </si>
   <si>
-    <t>Gửi lại file này + toàn bộ ảnh cho bên kỹ thuật để nạp vào hệ thống.</t>
+    <t>Gửi lại file này + toàn bộ ảnh cho đội kỹ thuật để nạp vào hệ thống.</t>
   </si>
   <si>
     <t>Mục thông tin</t>
@@ -68,13 +80,10 @@
     <t>Tên thương hiệu (Tiếng Việt) *</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Nội Thất Phương Đông</t>
   </si>
   <si>
-    <t>Tên thương hiệu (Tiếng Anh) *</t>
+    <t>Tên thương hiệu (Tiếng Anh)</t>
   </si>
   <si>
     <t>Phuong Dong Furniture</t>
@@ -146,6 +155,12 @@
     <t>https://instagram.com/cuahang</t>
   </si>
   <si>
+    <t>Website / Liên kết khác (URL)</t>
+  </si>
+  <si>
+    <t>https://cuahang.vn</t>
+  </si>
+  <si>
     <t>4. SEO MẶC ĐỊNH (hiển thị trên Google &amp; khi chia sẻ link)</t>
   </si>
   <si>
@@ -167,7 +182,7 @@
     <t>Mô tả SEO mặc định (Tiếng Anh)</t>
   </si>
   <si>
-    <t>Ảnh chia sẻ mặc định (tên file)</t>
+    <t>Ảnh chia sẻ mặc định (OG) (tên file)</t>
   </si>
   <si>
     <t>og-image.jpg</t>
@@ -285,7 +300,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -296,46 +311,22 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF784212"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color rgb="FF10233A"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC0392B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="10"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF667788"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1A2530"/>
-      <sz val="10"/>
+      <color rgb="FF5b6b7b"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,13 +358,8 @@
         <fgColor rgb="FFF4F8FC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -381,68 +367,44 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCBD5E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCBD5E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCBD5E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCBD5E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,65 +745,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="12"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="34" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -855,467 +833,391 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="55" customWidth="1"/>
+    <col min="1" max="1" width="42" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>18</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B3" s="9"/>
       <c r="C3" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="9"/>
       <c r="C5" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>18</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B8" s="9"/>
       <c r="C8" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>18</v>
-      </c>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="9"/>
       <c r="C12" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="9"/>
       <c r="C14" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="9"/>
       <c r="C16" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="10" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="B20" s="6"/>
+      <c r="C20" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="10" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="12" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="12" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="B29" s="9"/>
+      <c r="C29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="10" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="36" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="12" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="40" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="12" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="10" t="s">
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="B42" s="9"/>
+      <c r="C42" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="12" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>88</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1323,119 +1225,104 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
-  <dataValidations count="36">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Địa chỉ trụ sở chính" prompt="Địa chỉ đầy đủ trụ sở/văn phòng chính." sqref="B10">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Facebook (URL)" prompt="Link trang Facebook, bắt đầu bằng https://" sqref="B12">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Zalo (URL)" prompt="Link Zalo OA hoặc https://zalo.me/số điện thoại" sqref="B13">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="YouTube (URL)" prompt="Link kênh YouTube." sqref="B14">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="TikTok (URL)" prompt="Link kênh TikTok." sqref="B15">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Instagram (URL)" prompt="Link Instagram." sqref="B16">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề SEO mặc định (Tiếng Việt)" prompt="Tiêu đề hiển thị trên Google (khoảng 50-60 ký tự)." sqref="B18">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Mô tả SEO mặc định (Tiếng Việt)" prompt="Mô tả ngắn dưới tiêu đề Google (khoảng 150-160 ký tự)." sqref="B19">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề SEO mặc định (Tiếng Anh)" prompt="Bản tiếng Anh (tuỳ chọn)." sqref="B20">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Mô tả SEO mặc định (Tiếng Anh)" prompt="Bản tiếng Anh (tuỳ chọn)." sqref="B21">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Ảnh chia sẻ mặc định (tên file)" prompt="Ảnh hiện khi chia sẻ link lên MXH (1200x630). Gửi kèm file." sqref="B22">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Tiêu đề (VI)" prompt="Câu tiêu đề lớn của slide 1." sqref="B24">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Tiêu đề (EN)" prompt="Bản tiếng Anh (tuỳ chọn)." sqref="B25">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Mô tả (VI)" prompt="Câu mô tả phụ." sqref="B26">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Nhãn nút (CTA)" prompt="Chữ trên nút bấm." sqref="B27">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Link nút (CTA)" prompt="Đường dẫn khi bấm nút." sqref="B28">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Ảnh (tên file)" prompt="Ảnh nền slide 1 (ngang, &gt;=1920x1080)." sqref="B29">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tên thương hiệu (Tiếng Việt)" prompt="Tên cửa hàng/công ty hiển thị trên website." sqref="B3">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 2 - Tiêu đề (VI)" prompt="Để trống nếu chỉ dùng 1 slide." sqref="B30">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 2 - Mô tả (VI)" sqref="B31">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 2 - Ảnh (tên file)" sqref="B32">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 3 - Tiêu đề (VI)" prompt="Để trống nếu không dùng." sqref="B33">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 3 - Mô tả (VI)" sqref="B34">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 3 - Ảnh (tên file)" sqref="B35">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề câu chuyện (VI)" prompt="Tiêu đề khối giới thiệu thương hiệu." sqref="B37">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Đoạn dẫn câu chuyện (VI)" prompt="1-2 câu giới thiệu ngắn." sqref="B38">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Ảnh minh hoạ (tên file)" prompt="Ảnh bên cạnh phần giới thiệu." sqref="B39">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tên thương hiệu (Tiếng Anh)" prompt="Tên tiếng Anh (nếu không có, ghi lại tên tiếng Việt)." sqref="B4">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 1 - Con số" prompt="Ví dụ: 15+ , 5000+ ..." sqref="B41">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 1 - Mô tả" prompt="Ý nghĩa con số." sqref="B42">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 2 - Con số" sqref="B43">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 2 - Mô tả" sqref="B44">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Logo (tên file)" prompt="Gửi kèm file logo, ghi tên file. Ưu tiên PNG nền trong suốt." sqref="B5">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Favicon (tên file)" prompt="Icon nhỏ hiển thị trên tab trình duyệt (32x32 hoặc .ico)." sqref="B6">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Hotline tư vấn" prompt="Số điện thoại chính hiển thị toàn site." sqref="B8">
-      <formula1>=TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Email nhận báo giá" prompt="Email nhận thông báo khi khách gửi yêu cầu báo giá." sqref="B9">
-      <formula1>=TRUE</formula1>
+  <dataValidations count="31">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Địa chỉ trụ sở" prompt="Địa chỉ đầy đủ trụ sở/văn phòng chính (tuỳ chọn)." sqref="B10">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Facebook" prompt="Link trang Facebook, bắt đầu https://" sqref="B12">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Zalo" prompt="Link Zalo OA hoặc https://zalo.me/số điện thoại" sqref="B13">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="YouTube" prompt="Link kênh YouTube." sqref="B14">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="TikTok" prompt="Link kênh TikTok." sqref="B15">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Instagram" prompt="Link Instagram." sqref="B16">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Website / Liên kết khác" prompt="Website chính hoặc liên kết bổ sung (tuỳ chọn)." sqref="B17">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề SEO (VI)" prompt="Khoảng 50-60 ký tự, có tên thương hiệu. Bắt buộc." sqref="B19">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Mô tả SEO (VI)" prompt="Khoảng 150-160 ký tự. Bắt buộc." sqref="B20">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề SEO (EN)" prompt="Tuỳ chọn; để trống sẽ dùng bản tiếng Việt." sqref="B21">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Mô tả SEO (EN)" prompt="Tuỳ chọn; để trống sẽ dùng bản tiếng Việt." sqref="B22">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Ảnh chia sẻ (OG)" prompt="Ảnh hiện khi chia sẻ link lên MXH (1200x630). Gửi kèm file." sqref="B23">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Tiêu đề (VI)" prompt="Câu tiêu đề lớn của slide 1." sqref="B25">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Tiêu đề (EN)" prompt="Tuỳ chọn." sqref="B26">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Mô tả (VI)" prompt="Câu mô tả phụ." sqref="B27">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Nhãn nút" prompt="Chữ trên nút bấm." sqref="B28">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Link nút" prompt="Đường dẫn khi bấm nút, vd /products." sqref="B29">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tên thương hiệu (VI)" prompt="Tên cửa hàng/công ty hiển thị trên website. Bắt buộc." sqref="B3">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 1 - Ảnh" prompt="Ảnh nền slide 1 (ngang, &gt;=1920x1080)." sqref="B30">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 2 - Tiêu đề (VI)" prompt="Để trống nếu chỉ dùng 1 slide." sqref="B31">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Slide 3 - Tiêu đề (VI)" prompt="Để trống nếu không dùng." sqref="B34">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tiêu đề câu chuyện" prompt="Tiêu đề khối giới thiệu thương hiệu." sqref="B38">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Đoạn dẫn câu chuyện" prompt="1-2 câu giới thiệu ngắn." sqref="B39">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Tên thương hiệu (EN)" prompt="Tuỳ chọn; để trống sẽ dùng bản tiếng Việt." sqref="B4">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Ảnh minh hoạ" prompt="Ảnh bên cạnh phần giới thiệu." sqref="B40">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 1 - Con số" prompt="Ví dụ: 15+, 5000+ ..." sqref="B42">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Huy hiệu 1 - Mô tả" prompt="Ý nghĩa con số." sqref="B43">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Logo" prompt="Ghi tên file logo, gửi kèm. Ưu tiên PNG nền trong suốt." sqref="B5">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Favicon" prompt="Icon nhỏ trên tab trình duyệt (32x32 hoặc .ico)." sqref="B6">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Hotline" prompt="Số điện thoại chính hiển thị toàn site (8–15 chữ số). Bắt buộc." sqref="B8">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Email nhận báo giá" prompt="Email hiển thị liên hệ + nhận thông báo khi khách gửi yêu cầu báo giá. Bắt buộc." sqref="B9">
+      <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
